--- a/artfynd/A 47267-2022 artfynd.xlsx
+++ b/artfynd/A 47267-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120019782</v>
+        <v>120019783</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120019783</v>
+        <v>120019782</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 47267-2022 artfynd.xlsx
+++ b/artfynd/A 47267-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120019783</v>
+        <v>120019782</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120019782</v>
+        <v>120019783</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 47267-2022 artfynd.xlsx
+++ b/artfynd/A 47267-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120019783</v>
+        <v>120019782</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120019782</v>
+        <v>120019783</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 47267-2022 artfynd.xlsx
+++ b/artfynd/A 47267-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120019782</v>
+        <v>120019783</v>
       </c>
       <c r="B2" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120019783</v>
+        <v>120019782</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 47267-2022 artfynd.xlsx
+++ b/artfynd/A 47267-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120019783</v>
+        <v>120019782</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120019782</v>
+        <v>120019783</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
